--- a/enrichissement-pharm/ig/StructureDefinition-fr-cda-commentaire-er.xlsx
+++ b/enrichissement-pharm/ig/StructureDefinition-fr-cda-commentaire-er.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2606" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2606" uniqueCount="309">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T05:36:05+00:00</t>
+    <t>2026-07-29T08:04:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -96,7 +96,7 @@
     <t>FHIR Version</t>
   </si>
   <si>
-    <t>4.0.1</t>
+    <t>5.0.0</t>
   </si>
   <si>
     <t>Kind</t>
@@ -414,9 +414,6 @@
     <t>ccdComment</t>
   </si>
   <si>
-    <t xml:space="preserve">Conformité Comment (CCD) </t>
-  </si>
-  <si>
     <t>Conformité Comment (CCD)</t>
   </si>
   <si>
@@ -897,7 +894,7 @@
     <t>Act.languageCode</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/all-languages|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/all-languages|5.0.0</t>
   </si>
   <si>
     <t>Act.subject</t>
@@ -2499,7 +2496,7 @@
         <v>129</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2570,10 +2567,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="B13" t="s" s="2">
         <v>131</v>
-      </c>
-      <c r="B13" t="s" s="2">
-        <v>132</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2671,10 +2668,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="B14" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="B14" t="s" s="2">
-        <v>134</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2774,10 +2771,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="B15" t="s" s="2">
         <v>135</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>136</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2877,10 +2874,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="B16" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>138</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2909,7 +2906,7 @@
       </c>
       <c r="L16" s="2"/>
       <c r="M16" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2921,7 +2918,7 @@
         <v>75</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>75</v>
@@ -2980,10 +2977,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="B17" t="s" s="2">
         <v>141</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>142</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3083,13 +3080,13 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B18" t="s" s="2">
         <v>121</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D18" t="s" s="2">
         <v>75</v>
@@ -3114,10 +3111,10 @@
         <v>96</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3188,10 +3185,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3289,10 +3286,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3392,10 +3389,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3495,10 +3492,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3527,7 +3524,7 @@
       </c>
       <c r="L22" s="2"/>
       <c r="M22" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3539,7 +3536,7 @@
         <v>75</v>
       </c>
       <c r="S22" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="T22" t="s" s="2">
         <v>75</v>
@@ -3598,10 +3595,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3701,13 +3698,13 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B24" t="s" s="2">
         <v>121</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>75</v>
@@ -3732,10 +3729,10 @@
         <v>96</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3806,10 +3803,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3907,10 +3904,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4010,10 +4007,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4113,10 +4110,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4145,7 +4142,7 @@
       </c>
       <c r="L28" s="2"/>
       <c r="M28" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4157,7 +4154,7 @@
         <v>75</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="T28" t="s" s="2">
         <v>75</v>
@@ -4216,10 +4213,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4319,10 +4316,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4336,7 +4333,7 @@
         <v>76</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>75</v>
@@ -4359,7 +4356,7 @@
         <v>75</v>
       </c>
       <c r="S30" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="T30" t="s" s="2">
         <v>75</v>
@@ -4378,7 +4375,7 @@
       </c>
       <c r="Y30" s="2"/>
       <c r="Z30" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>75</v>
@@ -4396,7 +4393,7 @@
         <v>75</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>76</v>
@@ -4416,10 +4413,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4433,7 +4430,7 @@
         <v>76</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>75</v>
@@ -4456,7 +4453,7 @@
         <v>75</v>
       </c>
       <c r="S31" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="T31" t="s" s="2">
         <v>75</v>
@@ -4475,7 +4472,7 @@
       </c>
       <c r="Y31" s="2"/>
       <c r="Z31" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>75</v>
@@ -4493,7 +4490,7 @@
         <v>75</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>76</v>
@@ -4513,10 +4510,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4592,7 +4589,7 @@
         <v>75</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -4612,10 +4609,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4691,7 +4688,7 @@
         <v>75</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -4711,10 +4708,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4728,7 +4725,7 @@
         <v>76</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>75</v>
@@ -4737,13 +4734,13 @@
         <v>75</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="L34" t="s" s="2">
-        <v>172</v>
-      </c>
       <c r="M34" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4770,11 +4767,11 @@
         <v>75</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Y34" s="2"/>
       <c r="Z34" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>75</v>
@@ -4792,7 +4789,7 @@
         <v>75</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>76</v>
@@ -4812,10 +4809,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4913,10 +4910,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4932,7 +4929,7 @@
         <v>76</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>75</v>
@@ -4945,7 +4942,7 @@
       </c>
       <c r="L36" s="2"/>
       <c r="M36" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4957,46 +4954,46 @@
         <v>75</v>
       </c>
       <c r="S36" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="T36" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U36" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V36" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W36" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X36" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y36" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z36" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA36" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB36" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD36" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE36" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF36" t="s" s="2">
         <v>178</v>
-      </c>
-      <c r="T36" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U36" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V36" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W36" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X36" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y36" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z36" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA36" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB36" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC36" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD36" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE36" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF36" t="s" s="2">
-        <v>179</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -5016,17 +5013,17 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E37" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F37" t="s" s="2">
         <v>76</v>
@@ -5035,7 +5032,7 @@
         <v>76</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>75</v>
@@ -5048,7 +5045,7 @@
       </c>
       <c r="L37" s="2"/>
       <c r="M37" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5060,46 +5057,46 @@
         <v>75</v>
       </c>
       <c r="S37" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="T37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF37" t="s" s="2">
         <v>183</v>
-      </c>
-      <c r="T37" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U37" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V37" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W37" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X37" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y37" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z37" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA37" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB37" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC37" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD37" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE37" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF37" t="s" s="2">
-        <v>184</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -5119,17 +5116,17 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E38" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F38" t="s" s="2">
         <v>81</v>
@@ -5151,7 +5148,7 @@
       </c>
       <c r="L38" s="2"/>
       <c r="M38" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5163,46 +5160,46 @@
         <v>75</v>
       </c>
       <c r="S38" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="T38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF38" t="s" s="2">
         <v>188</v>
-      </c>
-      <c r="T38" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U38" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V38" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W38" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X38" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y38" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z38" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA38" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB38" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC38" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD38" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE38" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF38" t="s" s="2">
-        <v>189</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -5222,17 +5219,17 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E39" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F39" t="s" s="2">
         <v>81</v>
@@ -5254,7 +5251,7 @@
       </c>
       <c r="L39" s="2"/>
       <c r="M39" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5305,7 +5302,7 @@
         <v>75</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -5325,17 +5322,17 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E40" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F40" t="s" s="2">
         <v>81</v>
@@ -5344,7 +5341,7 @@
         <v>76</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>75</v>
@@ -5357,7 +5354,7 @@
       </c>
       <c r="L40" s="2"/>
       <c r="M40" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5369,46 +5366,46 @@
         <v>75</v>
       </c>
       <c r="S40" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="T40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF40" t="s" s="2">
         <v>197</v>
-      </c>
-      <c r="T40" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U40" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V40" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W40" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X40" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y40" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z40" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA40" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB40" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC40" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD40" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE40" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF40" t="s" s="2">
-        <v>198</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -5428,10 +5425,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5454,11 +5451,11 @@
         <v>75</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="L41" s="2"/>
       <c r="M41" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5509,7 +5506,7 @@
         <v>75</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -5529,10 +5526,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5559,7 +5556,7 @@
       </c>
       <c r="L42" s="2"/>
       <c r="M42" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5610,7 +5607,7 @@
         <v>75</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -5630,39 +5627,39 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E43" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="F43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K43" t="s" s="2">
         <v>207</v>
-      </c>
-      <c r="F43" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G43" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H43" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I43" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J43" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K43" t="s" s="2">
-        <v>208</v>
       </c>
       <c r="L43" s="2"/>
       <c r="M43" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -5713,7 +5710,7 @@
         <v>75</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -5733,17 +5730,17 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E44" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F44" t="s" s="2">
         <v>81</v>
@@ -5761,11 +5758,11 @@
         <v>75</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="L44" s="2"/>
       <c r="M44" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -5816,7 +5813,7 @@
         <v>75</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -5836,17 +5833,17 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E45" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F45" t="s" s="2">
         <v>81</v>
@@ -5864,11 +5861,11 @@
         <v>75</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="L45" s="2"/>
       <c r="M45" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -5919,7 +5916,7 @@
         <v>75</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -5939,10 +5936,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -5956,7 +5953,7 @@
         <v>76</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>75</v>
@@ -5965,13 +5962,13 @@
         <v>75</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6022,7 +6019,7 @@
         <v>75</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -6042,10 +6039,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6143,17 +6140,17 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E48" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F48" t="s" s="2">
         <v>81</v>
@@ -6175,7 +6172,7 @@
       </c>
       <c r="L48" s="2"/>
       <c r="M48" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -6206,25 +6203,25 @@
       </c>
       <c r="Y48" s="2"/>
       <c r="Z48" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="AA48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF48" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="AA48" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB48" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC48" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD48" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE48" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF48" t="s" s="2">
-        <v>227</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -6244,39 +6241,39 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E49" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="F49" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G49" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K49" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="F49" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G49" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H49" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I49" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J49" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K49" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="L49" s="2"/>
       <c r="M49" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -6327,7 +6324,7 @@
         <v>75</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -6347,17 +6344,17 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E50" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F50" t="s" s="2">
         <v>81</v>
@@ -6379,7 +6376,7 @@
       </c>
       <c r="L50" s="2"/>
       <c r="M50" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -6410,25 +6407,25 @@
       </c>
       <c r="Y50" s="2"/>
       <c r="Z50" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF50" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="AA50" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB50" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC50" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD50" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE50" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF50" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -6448,17 +6445,17 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E51" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F51" t="s" s="2">
         <v>81</v>
@@ -6480,7 +6477,7 @@
       </c>
       <c r="L51" s="2"/>
       <c r="M51" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -6531,7 +6528,7 @@
         <v>75</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -6551,17 +6548,17 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E52" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F52" t="s" s="2">
         <v>81</v>
@@ -6583,7 +6580,7 @@
       </c>
       <c r="L52" s="2"/>
       <c r="M52" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -6610,29 +6607,29 @@
         <v>75</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Y52" s="2"/>
       <c r="Z52" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF52" t="s" s="2">
         <v>245</v>
-      </c>
-      <c r="AA52" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB52" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD52" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE52" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF52" t="s" s="2">
-        <v>246</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -6652,10 +6649,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6711,25 +6708,25 @@
       </c>
       <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF53" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="AA53" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB53" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC53" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD53" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE53" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF53" t="s" s="2">
-        <v>249</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -6749,10 +6746,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -6778,13 +6775,13 @@
         <v>103</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>253</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -6834,7 +6831,7 @@
         <v>75</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -6854,39 +6851,39 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E55" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="F55" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K55" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="F55" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G55" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H55" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I55" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J55" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K55" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="L55" s="2"/>
       <c r="M55" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -6937,7 +6934,7 @@
         <v>75</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -6957,17 +6954,17 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E56" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F56" t="s" s="2">
         <v>81</v>
@@ -6985,11 +6982,11 @@
         <v>75</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="L56" s="2"/>
       <c r="M56" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -7040,19 +7037,19 @@
         <v>75</v>
       </c>
       <c r="AF56" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
         <v>263</v>
-      </c>
-      <c r="AG56" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH56" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI56" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ56" t="s" s="2">
-        <v>264</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>75</v>
@@ -7060,10 +7057,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7077,7 +7074,7 @@
         <v>76</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>75</v>
@@ -7089,10 +7086,10 @@
         <v>92</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>266</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>267</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -7123,7 +7120,7 @@
       </c>
       <c r="Y57" s="2"/>
       <c r="Z57" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>75</v>
@@ -7141,7 +7138,7 @@
         <v>75</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -7161,10 +7158,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7262,10 +7259,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7294,7 +7291,7 @@
       </c>
       <c r="L59" s="2"/>
       <c r="M59" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -7306,7 +7303,7 @@
         <v>75</v>
       </c>
       <c r="S59" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="T59" t="s" s="2">
         <v>75</v>
@@ -7345,7 +7342,7 @@
         <v>75</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -7365,17 +7362,17 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E60" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F60" t="s" s="2">
         <v>81</v>
@@ -7397,7 +7394,7 @@
       </c>
       <c r="L60" s="2"/>
       <c r="M60" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -7448,7 +7445,7 @@
         <v>75</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -7468,17 +7465,17 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E61" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F61" t="s" s="2">
         <v>81</v>
@@ -7500,7 +7497,7 @@
       </c>
       <c r="L61" s="2"/>
       <c r="M61" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -7551,7 +7548,7 @@
         <v>75</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -7571,17 +7568,17 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E62" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F62" t="s" s="2">
         <v>81</v>
@@ -7603,7 +7600,7 @@
       </c>
       <c r="L62" s="2"/>
       <c r="M62" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -7654,7 +7651,7 @@
         <v>75</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -7674,17 +7671,17 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E63" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F63" t="s" s="2">
         <v>81</v>
@@ -7706,7 +7703,7 @@
       </c>
       <c r="L63" s="2"/>
       <c r="M63" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -7757,7 +7754,7 @@
         <v>75</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -7777,10 +7774,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -7803,11 +7800,11 @@
         <v>75</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="L64" s="2"/>
       <c r="M64" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -7858,7 +7855,7 @@
         <v>75</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -7878,10 +7875,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -7908,7 +7905,7 @@
       </c>
       <c r="L65" s="2"/>
       <c r="M65" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -7959,7 +7956,7 @@
         <v>75</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -7979,39 +7976,39 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E66" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="F66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K66" t="s" s="2">
         <v>207</v>
-      </c>
-      <c r="F66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H66" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I66" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J66" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K66" t="s" s="2">
-        <v>208</v>
       </c>
       <c r="L66" s="2"/>
       <c r="M66" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -8062,7 +8059,7 @@
         <v>75</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -8082,39 +8079,39 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E67" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="F67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K67" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="F67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H67" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I67" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J67" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K67" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="L67" s="2"/>
       <c r="M67" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -8165,7 +8162,7 @@
         <v>75</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -8185,17 +8182,17 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E68" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F68" t="s" s="2">
         <v>81</v>
@@ -8213,11 +8210,11 @@
         <v>75</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="L68" s="2"/>
       <c r="M68" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -8268,7 +8265,7 @@
         <v>75</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -8288,10 +8285,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8314,7 +8311,7 @@
         <v>75</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="L69" s="2"/>
       <c r="M69" s="2"/>
@@ -8367,7 +8364,7 @@
         <v>75</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -8387,10 +8384,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8413,7 +8410,7 @@
         <v>75</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="L70" s="2"/>
       <c r="M70" s="2"/>
@@ -8442,11 +8439,11 @@
         <v>75</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Y70" s="2"/>
       <c r="Z70" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>75</v>
@@ -8464,7 +8461,7 @@
         <v>75</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -8484,10 +8481,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8543,7 +8540,7 @@
       </c>
       <c r="Y71" s="2"/>
       <c r="Z71" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>75</v>
@@ -8561,7 +8558,7 @@
         <v>75</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -8581,10 +8578,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8607,7 +8604,7 @@
         <v>75</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="L72" s="2"/>
       <c r="M72" s="2"/>
@@ -8660,7 +8657,7 @@
         <v>75</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -8680,10 +8677,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -8706,7 +8703,7 @@
         <v>75</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="L73" s="2"/>
       <c r="M73" s="2"/>
@@ -8759,7 +8756,7 @@
         <v>75</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -8779,10 +8776,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -8805,7 +8802,7 @@
         <v>75</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="L74" s="2"/>
       <c r="M74" s="2"/>
@@ -8858,7 +8855,7 @@
         <v>75</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -8878,10 +8875,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -8904,7 +8901,7 @@
         <v>75</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="L75" s="2"/>
       <c r="M75" s="2"/>
@@ -8957,7 +8954,7 @@
         <v>75</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -8977,10 +8974,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9003,7 +9000,7 @@
         <v>75</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="L76" s="2"/>
       <c r="M76" s="2"/>
@@ -9056,7 +9053,7 @@
         <v>75</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -9076,10 +9073,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9102,7 +9099,7 @@
         <v>75</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="L77" s="2"/>
       <c r="M77" s="2"/>
@@ -9155,7 +9152,7 @@
         <v>75</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -9175,10 +9172,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9201,7 +9198,7 @@
         <v>75</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="L78" s="2"/>
       <c r="M78" s="2"/>
@@ -9254,7 +9251,7 @@
         <v>75</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -9274,10 +9271,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9300,7 +9297,7 @@
         <v>75</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="L79" s="2"/>
       <c r="M79" s="2"/>
@@ -9353,7 +9350,7 @@
         <v>75</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -9373,10 +9370,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9399,7 +9396,7 @@
         <v>75</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="L80" s="2"/>
       <c r="M80" s="2"/>
@@ -9452,7 +9449,7 @@
         <v>75</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
@@ -9472,10 +9469,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -9498,7 +9495,7 @@
         <v>75</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="L81" s="2"/>
       <c r="M81" s="2"/>
@@ -9551,7 +9548,7 @@
         <v>75</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -9571,10 +9568,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -9597,7 +9594,7 @@
         <v>75</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="L82" s="2"/>
       <c r="M82" s="2"/>
@@ -9650,7 +9647,7 @@
         <v>75</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>

--- a/enrichissement-pharm/ig/StructureDefinition-fr-cda-commentaire-er.xlsx
+++ b/enrichissement-pharm/ig/StructureDefinition-fr-cda-commentaire-er.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T08:04:35+00:00</t>
+    <t>2026-07-29T08:58:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/enrichissement-pharm/ig/StructureDefinition-fr-cda-commentaire-er.xlsx
+++ b/enrichissement-pharm/ig/StructureDefinition-fr-cda-commentaire-er.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T08:58:09+00:00</t>
+    <t>2026-07-29T09:37:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/enrichissement-pharm/ig/StructureDefinition-fr-cda-commentaire-er.xlsx
+++ b/enrichissement-pharm/ig/StructureDefinition-fr-cda-commentaire-er.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T09:37:21+00:00</t>
+    <t>2026-08-03T10:14:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
